--- a/files/港岛-湾仔-Woodis.xlsx
+++ b/files/港岛-湾仔-Woodis.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Woodis 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1905,7 +1769,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2101,7 +1965,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2147,7 +2011,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2193,7 +2057,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2239,7 +2103,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2385,7 +2249,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2431,7 +2295,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2477,7 +2341,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2523,7 +2387,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2569,7 +2433,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2665,7 +2529,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2711,7 +2575,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2757,7 +2621,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2803,7 +2667,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2849,7 +2713,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2895,7 +2759,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2991,7 +2855,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3083,7 +2947,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3129,7 +2993,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3175,7 +3039,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3221,7 +3085,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3367,7 +3231,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3413,7 +3277,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3459,7 +3323,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3505,7 +3369,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3551,7 +3415,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3647,7 +3511,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3693,7 +3557,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3739,7 +3603,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3785,7 +3649,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3831,7 +3695,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3877,7 +3741,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3973,7 +3837,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -4019,7 +3883,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -4065,7 +3929,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -4111,7 +3975,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4157,7 +4021,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4203,7 +4067,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4299,7 +4163,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4345,7 +4209,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4391,7 +4255,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4437,7 +4301,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4483,7 +4347,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4529,7 +4393,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4625,7 +4489,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4671,7 +4535,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4717,7 +4581,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4763,7 +4627,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4855,7 +4719,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4951,7 +4815,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4997,7 +4861,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -5043,7 +4907,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -5089,7 +4953,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5135,7 +4999,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5181,7 +5045,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5277,7 +5141,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5369,7 +5233,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5507,7 +5371,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5603,7 +5467,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5649,7 +5513,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5741,7 +5605,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5787,7 +5651,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5833,7 +5697,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5879,7 +5743,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5925,7 +5789,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -5971,7 +5835,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -6155,7 +6019,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6201,7 +6065,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6247,7 +6111,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6293,7 +6157,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6339,7 +6203,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6431,7 +6295,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6477,7 +6341,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6523,7 +6387,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6569,7 +6433,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6615,7 +6479,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6661,7 +6525,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6707,7 +6571,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6753,7 +6617,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6799,7 +6663,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6845,7 +6709,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -6891,7 +6755,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6937,7 +6801,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -7179,7 +7043,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7225,7 +7089,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7271,7 +7135,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7317,7 +7181,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -7463,7 +7327,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7509,7 +7373,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -7555,7 +7419,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7601,7 +7465,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7647,7 +7511,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -7843,7 +7707,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -7889,7 +7753,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7935,7 +7799,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -8181,7 +8045,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -8227,7 +8091,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -8473,7 +8337,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -8519,7 +8383,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -8591,1664 +8455,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Woodis - Woodis 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>167 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>105 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>57 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1016呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 794呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-      <c r="H6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 1016呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="17" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
-      <c r="H7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-$971万
-$25,753/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-$961万
-$25,499/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-$847万
-$24,687/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-$862万
-$24,906/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$1,217万
-$28,236/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-$1,875万
-$31,358/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-$922万
-$24,447/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-$831万
-$24,217/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-$900万
-$26,002/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$1,177万
-$27,316/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H12" s="18" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-$1,270万
-$29,819/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-$1,820万
-$30,441/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-$945万
-$25,073/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-$809万
-$23,600/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-$840万
-$24,282/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$1,137万
-$26,373/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-$1,169万
-$27,438/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-$939万
-$24,904/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-$770万
-$22,464/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-$782万
-$22,598/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$1,119万
-$25,965/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-$1,194万
-$28,039/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-$1,711万
-$28,607/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-$933万
-$24,735/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-$799万
-$23,283/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-$774万
-$22,375/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$1,108万
-$25,705/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-$1,121万
-$26,326/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-$1,545万
-$25,843/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-$897万
-$23,788/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-$758万
-$22,085/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-$766万
-$22,149/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$1,097万
-$25,447/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-$1,107万
-$25,976/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-$1,524万
-$25,480/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-$967万
-$25,655/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-$750万
-$21,857/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-$759万
-$21,923/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$1,086万
-$25,189/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-$1,061万
-$24,903/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-$1,552万
-$25,952/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-$884万
-$23,461/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-$742万
-$21,632/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-$751万
-$21,697/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$1,041万
-$24,142/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-$1,081万
-$25,365/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-$1,482万
-$24,785/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-$905万
-$23,993/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-$801万
-$23,347/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-$746万
-$21,548/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$1,030万
-$23,892/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-$1,077万
-$25,280/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-$1,472万
-$24,611/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-$872万
-$23,132/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-$755万
-$22,024/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-$740万
-$21,397/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$1,023万
-$23,726/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-$1,025万
-$24,058/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-$1,509万
-$25,234/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-$866万
-$22,966/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-$790万
-$23,017/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-$799万
-$23,095/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$1,015万
-$23,557/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-$1,045万
-$24,533/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-$1,509万
-$25,228/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-$720万
-$25,533/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-$885万
-$23,485/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-$721万
-$21,026/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-$730万
-$21,096/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$1,008万
-$23,390/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-$1,010万
-$23,719/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-$1,425万
-$23,829/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-$715万
-$25,347/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-$853万
-$22,639/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="19" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-$778万
-$22,688/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F23" s="19" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-$782万
-$22,604/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$1,030万
-$23,895/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H23" s="18" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-$1,030万
-$24,185/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-$1,399万
-$23,394/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-$676万
-$23,966/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-$874万
-$23,193/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-$734万
-$21,396/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-$738万
-$21,320/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$983万
-$22,806/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-$996万
-$23,382/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-$1,373万
-$22,965/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-$710万
-$25,185/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-$844万
-$22,395/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-$706万
-$20,570/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-$705万
-$20,389/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$1,000万
-$23,206/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H25" s="18" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-$989万
-$23,212/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-$1,347万
-$22,525/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-$671万
-$23,806/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$951万
-$22,054/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H26" s="18" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-$1,014万
-$23,795/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-$1,321万
-$22,089/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-$669万
-$23,740/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-$865万
-$22,954/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$943万
-$21,888/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H27" s="18" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-$1,006万
-$23,621/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-$1,337万
-$22,360/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-$664万
-$23,561/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$936万
-$21,719/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-$999万
-$23,447/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 598呎 (3房)
-$1,310万
-$21,912/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 282呎 (1房)
-$659万
-$23,359/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 343呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 346呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H29" s="18" t="inlineStr">
-        <is>
-          <t>G | 426呎 (2房)
-$994万
-$23,324/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 560呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>B | 244呎 (1房)
-$662万
-$27,143/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>C | 339呎 (2房)
-$930万
-$27,423/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>F | 393呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>G | 388呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-湾仔-Woodis.xlsx
+++ b/files/港岛-湾仔-Woodis.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Woodis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,95 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +141,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +222,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +652,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -8455,4 +8633,1664 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Woodis 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1016呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 794呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1016呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+$971万
+$25,753/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+$961万
+$25,499/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+$847万
+$24,687/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+$862万
+$24,906/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$1217万
+$28,236/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+$1875万
+$31,358/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+$922万
+$24,447/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+$831万
+$24,217/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+$900万
+$26,002/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$1177万
+$27,316/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+$1270万
+$29,819/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+$1820万
+$30,441/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+$945万
+$25,073/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+$809万
+$23,600/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+$840万
+$24,282/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$1137万
+$26,373/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+$1169万
+$27,438/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+$939万
+$24,904/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+$770万
+$22,464/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+$782万
+$22,598/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$1119万
+$25,965/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+$1194万
+$28,039/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+$1711万
+$28,607/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+$933万
+$24,735/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+$799万
+$23,283/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+$774万
+$22,375/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$1108万
+$25,705/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+$1121万
+$26,326/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+$1545万
+$25,843/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+$897万
+$23,788/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+$758万
+$22,085/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+$766万
+$22,149/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$1097万
+$25,447/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+$1107万
+$25,976/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+$1524万
+$25,480/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+$967万
+$25,655/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+$750万
+$21,857/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+$759万
+$21,923/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$1086万
+$25,189/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+$1061万
+$24,903/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+$1552万
+$25,952/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+$884万
+$23,461/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+$742万
+$21,632/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+$751万
+$21,697/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$1041万
+$24,142/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+$1081万
+$25,365/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+$1482万
+$24,785/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+$905万
+$23,993/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+$801万
+$23,347/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+$746万
+$21,548/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$1030万
+$23,892/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+$1077万
+$25,280/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+$1472万
+$24,611/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+$872万
+$23,132/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+$755万
+$22,024/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+$740万
+$21,397/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$1023万
+$23,726/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+$1025万
+$24,058/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+$1509万
+$25,234/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+$866万
+$22,966/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+$790万
+$23,017/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+$799万
+$23,095/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$1015万
+$23,557/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+$1045万
+$24,533/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+$1509万
+$25,228/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+$720万
+$25,533/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+$885万
+$23,485/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+$721万
+$21,026/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+$730万
+$21,096/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$1008万
+$23,390/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+$1010万
+$23,719/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+$1425万
+$23,829/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+$715万
+$25,347/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+$853万
+$22,639/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+$778万
+$22,688/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+$782万
+$22,604/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$1030万
+$23,895/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+$1030万
+$24,185/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+$1399万
+$23,394/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+$676万
+$23,966/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+$874万
+$23,193/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+$734万
+$21,396/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+$738万
+$21,320/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$983万
+$22,806/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+$996万
+$23,382/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+$1373万
+$22,965/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+$710万
+$25,185/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+$844万
+$22,395/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+$706万
+$20,570/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+$705万
+$20,389/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$1000万
+$23,206/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+$989万
+$23,212/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+$1347万
+$22,525/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+$671万
+$23,806/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$951万
+$22,054/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+$1014万
+$23,795/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+$1321万
+$22,089/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+$669万
+$23,740/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+$865万
+$22,954/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$943万
+$21,888/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+$1006万
+$23,621/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+$1337万
+$22,360/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+$664万
+$23,561/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$936万
+$21,719/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+$999万
+$23,447/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 598呎 (3房)
+$1310万
+$21,912/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 282呎 (1房)
+$659万
+$23,359/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 343呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 346呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>G | 426呎 (2房)
+$994万
+$23,324/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 560呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 244呎 (1房)
+$662万
+$27,143/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 339呎 (2房)
+$930万
+$27,423/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>F | 393呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>G | 388呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-湾仔-Woodis.xlsx
+++ b/files/港岛-湾仔-Woodis.xlsx
@@ -652,7 +652,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-湾仔-Woodis.xlsx
+++ b/files/港岛-湾仔-Woodis.xlsx
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J169"/>
+  <dimension ref="A1:N169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -655,6 +655,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -712,6 +716,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -762,6 +786,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -812,6 +856,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -862,6 +926,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -912,6 +996,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -962,6 +1066,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1012,6 +1136,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1062,6 +1206,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1112,6 +1276,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1162,6 +1346,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1212,6 +1416,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1262,6 +1486,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1312,6 +1556,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1362,6 +1626,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1412,6 +1696,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1462,6 +1766,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1512,6 +1836,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1562,6 +1906,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1612,6 +1976,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1662,6 +2046,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1712,6 +2116,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1762,6 +2186,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1812,6 +2256,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1862,6 +2326,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1912,6 +2396,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1958,6 +2462,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>9709000</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>25753</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2008,6 +2528,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2058,6 +2598,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2108,6 +2668,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2154,6 +2734,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>12169700</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>28236</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2200,6 +2796,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>8617600</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>24906</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2246,6 +2858,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>8467600</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>24687</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2292,6 +2920,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>9613000</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>25499</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2342,6 +2986,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2392,6 +3056,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2438,6 +3122,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>12703100</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>29819</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2484,6 +3184,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>11773200</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>27316</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2530,6 +3246,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>8996700</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>26002</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2576,6 +3308,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>8306600</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>24217</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2622,6 +3370,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>9216500</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>24447</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2672,6 +3436,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2718,6 +3502,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>18752000</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>31358</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2764,6 +3564,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>11688600</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>27438</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2810,6 +3626,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>11366600</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>26373</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2856,6 +3688,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>8401400</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>24282</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2902,6 +3750,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>8094700</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>23600</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2948,6 +3812,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>9452500</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>25073</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2998,6 +3878,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3044,6 +3944,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>18203900</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>30441</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3090,6 +4006,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>11944500</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>28039</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3136,6 +4068,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>11191000</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>25965</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3182,6 +4130,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>7819000</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>22598</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3228,6 +4192,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>7705000</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>22464</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3274,6 +4254,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>9388800</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>24904</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3324,6 +4320,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3374,6 +4390,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3420,6 +4456,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>11214700</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>26326</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3466,6 +4518,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>11078900</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>25705</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3512,6 +4580,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>7741800</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>22375</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3558,6 +4642,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>7986200</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>23283</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3604,6 +4704,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>9325200</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>24735</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3654,6 +4770,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3700,6 +4836,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>17106900</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>28607</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3746,6 +4898,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>11065600</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>25976</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3792,6 +4960,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>10967700</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>25447</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3838,6 +5022,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>7663600</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>22149</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3884,6 +5084,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>7575200</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>22085</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3930,6 +5146,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>8968100</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>23788</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3980,6 +5212,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4026,6 +5278,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>15454100</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>25843</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4072,6 +5340,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>10608500</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>24903</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4118,6 +5402,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>10856600</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>25189</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4164,6 +5464,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>7585400</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>21923</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4210,6 +5526,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>7497000</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>21857</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4256,6 +5588,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>9671800</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>25655</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4306,6 +5654,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4352,6 +5720,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>15237000</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>25480</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4398,6 +5782,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>10805300</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>25365</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4444,6 +5844,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>10405200</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>24142</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4490,6 +5906,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>7507200</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>21697</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4536,6 +5968,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>7419800</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>21632</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4582,6 +6030,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>8844800</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>23461</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4632,6 +6096,26 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4678,6 +6162,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>15519200</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>25952</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4724,6 +6224,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>10769200</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>25280</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4770,6 +6286,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>10297500</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>23892</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4816,6 +6348,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>7455600</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>21548</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4862,6 +6410,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>7367360</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>21479</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>120天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4908,6 +6472,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>9045400</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>23993</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4958,6 +6538,26 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5004,6 +6604,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>14821200</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>24785</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5050,6 +6666,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>10248800</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>24058</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5096,6 +6728,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>10225800</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>23726</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5142,6 +6790,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>7403200</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>21397</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5188,6 +6852,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>7554400</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>22024</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5234,6 +6914,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>8720600</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>23132</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5284,6 +6980,26 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5330,6 +7046,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>14717200</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>24611</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5376,6 +7108,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>10451200</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>24533</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5422,6 +7170,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>10153100</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>23557</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5468,6 +7232,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>7351720</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>21248</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>120天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5514,6 +7294,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>7263400</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>21176</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>120天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5560,6 +7356,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>8658100</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>22966</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5610,6 +7422,26 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5656,6 +7488,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>15089800</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>25234</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5702,6 +7550,22 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>10104300</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>23719</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5748,6 +7612,22 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>10081300</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>23390</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5794,6 +7674,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>7299200</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>21096</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5840,6 +7736,22 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>7211800</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>21026</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5886,6 +7798,22 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>8854000</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>23485</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5932,6 +7860,22 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>7200300</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>25533</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5978,6 +7922,22 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>15086400</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>25228</v>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6024,6 +7984,22 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>10303000</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>24185</v>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6070,6 +8046,22 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>10298900</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>23895</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6116,6 +8108,22 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>7195320</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>20796</v>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>120天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6162,6 +8170,22 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>7159440</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>20873</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>120天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6208,6 +8232,22 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>8534800</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>22639</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6254,6 +8294,22 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>7147900</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>25347</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6300,6 +8356,22 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>14249800</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>23829</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6346,6 +8418,22 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>9960800</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>23382</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6392,6 +8480,22 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>9829200</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>22806</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6438,6 +8542,22 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>7376700</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>21320</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6484,6 +8604,22 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>7338700</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>21396</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6530,6 +8666,22 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>8743600</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>23193</v>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6576,6 +8728,22 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>6758300</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>23966</v>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6622,6 +8790,22 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>13989500</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>23394</v>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6668,6 +8852,22 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>9888100</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>23212</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6714,6 +8914,22 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>10001600</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>23206</v>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6760,6 +8976,22 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>7054500</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>20389</v>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6806,6 +9038,22 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>7055400</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>20570</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6852,6 +9100,22 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>8442800</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>22395</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6898,6 +9162,22 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>7102300</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>25185</v>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6944,6 +9224,22 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>13732800</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>22965</v>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6990,6 +9286,22 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>10136500</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>23795</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7036,6 +9348,22 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>9505400</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>22054</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7086,6 +9414,26 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7136,6 +9484,26 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7186,6 +9554,26 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7232,6 +9620,22 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>6713200</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>23806</v>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7278,6 +9682,22 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>13469700</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>22525</v>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7324,6 +9744,22 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>10062400</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>23621</v>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7370,6 +9806,22 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>9433600</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>21888</v>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7420,6 +9872,26 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7470,6 +9942,26 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7516,6 +10008,22 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>8653500</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>22954</v>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7562,6 +10070,22 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>6694800</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>23740</v>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7608,6 +10132,22 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>13209300</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>22089</v>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7654,6 +10194,22 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>9988300</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>23447</v>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7700,6 +10256,22 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>9361000</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>21719</v>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7750,6 +10322,26 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7800,6 +10392,26 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7850,6 +10462,26 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7896,6 +10528,22 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>6644200</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>23561</v>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7942,6 +10590,22 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>13371200</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>22360</v>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7988,6 +10652,22 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>9936000</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>23324</v>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8038,6 +10718,26 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8088,6 +10788,26 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8138,6 +10858,26 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8188,6 +10928,26 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8234,6 +10994,22 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="5" t="n">
+        <v>6587200</v>
+      </c>
+      <c r="L161" s="5" t="n">
+        <v>23359</v>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8280,6 +11056,22 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>13103300</v>
+      </c>
+      <c r="L162" s="5" t="n">
+        <v>21912</v>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8330,6 +11122,26 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L163" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8380,6 +11192,26 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8430,6 +11262,26 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L165" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8480,6 +11332,26 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8526,6 +11398,22 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>9296400</v>
+      </c>
+      <c r="L167" s="5" t="n">
+        <v>27423</v>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8572,6 +11460,22 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>6623000</v>
+      </c>
+      <c r="L168" s="5" t="n">
+        <v>27143</v>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8622,13 +11526,33 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L169" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -8990,7 +11914,7 @@
           <t>C | 377呎 (2房)
 $971万
 $25,753/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -9053,7 +11977,7 @@
           <t>C | 377呎 (2房)
 $961万
 $25,499/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -9061,7 +11985,7 @@
           <t>D | 343呎 (2房)
 $847万
 $24,687/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -9069,7 +11993,7 @@
           <t>E | 346呎 (2房)
 $862万
 $24,906/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -9077,7 +12001,7 @@
           <t>F | 431呎 (2房)
 $1217万
 $28,236/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -9100,7 +12024,7 @@
           <t>A | 598呎 (3房)
 $1875万
 $31,358/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -9116,7 +12040,7 @@
           <t>C | 377呎 (2房)
 $922万
 $24,447/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -9124,7 +12048,7 @@
           <t>D | 343呎 (2房)
 $831万
 $24,217/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -9132,7 +12056,7 @@
           <t>E | 346呎 (2房)
 $900万
 $26,002/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -9140,7 +12064,7 @@
           <t>F | 431呎 (2房)
 $1177万
 $27,316/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -9148,7 +12072,7 @@
           <t>G | 426呎 (2房)
 $1270万
 $29,819/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
     </row>
@@ -9163,7 +12087,7 @@
           <t>A | 598呎 (3房)
 $1820万
 $30,441/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -9179,7 +12103,7 @@
           <t>C | 377呎 (2房)
 $945万
 $25,073/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -9187,7 +12111,7 @@
           <t>D | 343呎 (2房)
 $809万
 $23,600/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -9195,7 +12119,7 @@
           <t>E | 346呎 (2房)
 $840万
 $24,282/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -9203,7 +12127,7 @@
           <t>F | 431呎 (2房)
 $1137万
 $26,373/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -9211,7 +12135,7 @@
           <t>G | 426呎 (2房)
 $1169万
 $27,438/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
     </row>
@@ -9242,7 +12166,7 @@
           <t>C | 377呎 (2房)
 $939万
 $24,904/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -9250,7 +12174,7 @@
           <t>D | 343呎 (2房)
 $770万
 $22,464/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -9258,7 +12182,7 @@
           <t>E | 346呎 (2房)
 $782万
 $22,598/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -9266,7 +12190,7 @@
           <t>F | 431呎 (2房)
 $1119万
 $25,965/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -9274,7 +12198,7 @@
           <t>G | 426呎 (2房)
 $1194万
 $28,039/呎
-(25年-10月)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
     </row>
@@ -9289,7 +12213,7 @@
           <t>A | 598呎 (3房)
 $1711万
 $28,607/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -9305,7 +12229,7 @@
           <t>C | 377呎 (2房)
 $933万
 $24,735/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -9313,7 +12237,7 @@
           <t>D | 343呎 (2房)
 $799万
 $23,283/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -9321,7 +12245,7 @@
           <t>E | 346呎 (2房)
 $774万
 $22,375/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -9329,7 +12253,7 @@
           <t>F | 431呎 (2房)
 $1108万
 $25,705/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -9337,7 +12261,7 @@
           <t>G | 426呎 (2房)
 $1121万
 $26,326/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -9352,7 +12276,7 @@
           <t>A | 598呎 (3房)
 $1545万
 $25,843/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -9368,7 +12292,7 @@
           <t>C | 377呎 (2房)
 $897万
 $23,788/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -9376,7 +12300,7 @@
           <t>D | 343呎 (2房)
 $758万
 $22,085/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -9384,7 +12308,7 @@
           <t>E | 346呎 (2房)
 $766万
 $22,149/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -9392,7 +12316,7 @@
           <t>F | 431呎 (2房)
 $1097万
 $25,447/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -9400,7 +12324,7 @@
           <t>G | 426呎 (2房)
 $1107万
 $25,976/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -9415,7 +12339,7 @@
           <t>A | 598呎 (3房)
 $1524万
 $25,480/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -9431,7 +12355,7 @@
           <t>C | 377呎 (2房)
 $967万
 $25,655/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -9439,7 +12363,7 @@
           <t>D | 343呎 (2房)
 $750万
 $21,857/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -9447,7 +12371,7 @@
           <t>E | 346呎 (2房)
 $759万
 $21,923/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -9455,7 +12379,7 @@
           <t>F | 431呎 (2房)
 $1086万
 $25,189/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -9463,7 +12387,7 @@
           <t>G | 426呎 (2房)
 $1061万
 $24,903/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -9478,7 +12402,7 @@
           <t>A | 598呎 (3房)
 $1552万
 $25,952/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -9494,7 +12418,7 @@
           <t>C | 377呎 (2房)
 $884万
 $23,461/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -9502,7 +12426,7 @@
           <t>D | 343呎 (2房)
 $742万
 $21,632/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -9510,7 +12434,7 @@
           <t>E | 346呎 (2房)
 $751万
 $21,697/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -9518,7 +12442,7 @@
           <t>F | 431呎 (2房)
 $1041万
 $24,142/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -9526,7 +12450,7 @@
           <t>G | 426呎 (2房)
 $1081万
 $25,365/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -9541,7 +12465,7 @@
           <t>A | 598呎 (3房)
 $1482万
 $24,785/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -9557,7 +12481,7 @@
           <t>C | 377呎 (2房)
 $905万
 $23,993/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -9573,7 +12497,7 @@
           <t>E | 346呎 (2房)
 $746万
 $21,548/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -9581,7 +12505,7 @@
           <t>F | 431呎 (2房)
 $1030万
 $23,892/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -9589,7 +12513,7 @@
           <t>G | 426呎 (2房)
 $1077万
 $25,280/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -9604,7 +12528,7 @@
           <t>A | 598呎 (3房)
 $1472万
 $24,611/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -9620,7 +12544,7 @@
           <t>C | 377呎 (2房)
 $872万
 $23,132/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -9628,7 +12552,7 @@
           <t>D | 343呎 (2房)
 $755万
 $22,024/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -9636,7 +12560,7 @@
           <t>E | 346呎 (2房)
 $740万
 $21,397/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -9644,7 +12568,7 @@
           <t>F | 431呎 (2房)
 $1023万
 $23,726/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -9652,7 +12576,7 @@
           <t>G | 426呎 (2房)
 $1025万
 $24,058/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -9667,7 +12591,7 @@
           <t>A | 598呎 (3房)
 $1509万
 $25,234/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -9683,7 +12607,7 @@
           <t>C | 377呎 (2房)
 $866万
 $22,966/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -9707,7 +12631,7 @@
           <t>F | 431呎 (2房)
 $1015万
 $23,557/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -9715,7 +12639,7 @@
           <t>G | 426呎 (2房)
 $1045万
 $24,533/呎
-(25年-10月)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
     </row>
@@ -9730,7 +12654,7 @@
           <t>A | 598呎 (3房)
 $1509万
 $25,228/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -9738,7 +12662,7 @@
           <t>B | 282呎 (1房)
 $720万
 $25,533/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -9746,7 +12670,7 @@
           <t>C | 377呎 (2房)
 $885万
 $23,485/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -9754,7 +12678,7 @@
           <t>D | 343呎 (2房)
 $721万
 $21,026/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -9762,7 +12686,7 @@
           <t>E | 346呎 (2房)
 $730万
 $21,096/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -9770,7 +12694,7 @@
           <t>F | 431呎 (2房)
 $1008万
 $23,390/呎
-(25年-10月)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -9778,7 +12702,7 @@
           <t>G | 426呎 (2房)
 $1010万
 $23,719/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -9793,7 +12717,7 @@
           <t>A | 598呎 (3房)
 $1425万
 $23,829/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -9801,7 +12725,7 @@
           <t>B | 282呎 (1房)
 $715万
 $25,347/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -9809,7 +12733,7 @@
           <t>C | 377呎 (2房)
 $853万
 $22,639/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -9833,7 +12757,7 @@
           <t>F | 431呎 (2房)
 $1030万
 $23,895/呎
-(25年-10月)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -9841,7 +12765,7 @@
           <t>G | 426呎 (2房)
 $1030万
 $24,185/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -9856,7 +12780,7 @@
           <t>A | 598呎 (3房)
 $1399万
 $23,394/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -9864,7 +12788,7 @@
           <t>B | 282呎 (1房)
 $676万
 $23,966/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -9872,7 +12796,7 @@
           <t>C | 377呎 (2房)
 $874万
 $23,193/呎
-(25年-11月)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -9880,7 +12804,7 @@
           <t>D | 343呎 (2房)
 $734万
 $21,396/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -9888,7 +12812,7 @@
           <t>E | 346呎 (2房)
 $738万
 $21,320/呎
-(25年-10月)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -9896,7 +12820,7 @@
           <t>F | 431呎 (2房)
 $983万
 $22,806/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -9904,7 +12828,7 @@
           <t>G | 426呎 (2房)
 $996万
 $23,382/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
     </row>
@@ -9919,7 +12843,7 @@
           <t>A | 598呎 (3房)
 $1373万
 $22,965/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -9927,7 +12851,7 @@
           <t>B | 282呎 (1房)
 $710万
 $25,185/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -9935,7 +12859,7 @@
           <t>C | 377呎 (2房)
 $844万
 $22,395/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -9943,7 +12867,7 @@
           <t>D | 343呎 (2房)
 $706万
 $20,570/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -9951,7 +12875,7 @@
           <t>E | 346呎 (2房)
 $705万
 $20,389/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -9959,7 +12883,7 @@
           <t>F | 431呎 (2房)
 $1000万
 $23,206/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -9967,7 +12891,7 @@
           <t>G | 426呎 (2房)
 $989万
 $23,212/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
     </row>
@@ -9982,7 +12906,7 @@
           <t>A | 598呎 (3房)
 $1347万
 $22,525/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -9990,7 +12914,7 @@
           <t>B | 282呎 (1房)
 $671万
 $23,806/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -10022,7 +12946,7 @@
           <t>F | 431呎 (2房)
 $951万
 $22,054/呎
-(25年-10月)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -10030,7 +12954,7 @@
           <t>G | 426呎 (2房)
 $1014万
 $23,795/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
     </row>
@@ -10045,7 +12969,7 @@
           <t>A | 598呎 (3房)
 $1321万
 $22,089/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -10053,7 +12977,7 @@
           <t>B | 282呎 (1房)
 $669万
 $23,740/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -10061,7 +12985,7 @@
           <t>C | 377呎 (2房)
 $865万
 $22,954/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -10085,7 +13009,7 @@
           <t>F | 431呎 (2房)
 $943万
 $21,888/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -10093,7 +13017,7 @@
           <t>G | 426呎 (2房)
 $1006万
 $23,621/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -10108,7 +13032,7 @@
           <t>A | 598呎 (3房)
 $1337万
 $22,360/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -10116,7 +13040,7 @@
           <t>B | 282呎 (1房)
 $664万
 $23,561/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -10148,7 +13072,7 @@
           <t>F | 431呎 (2房)
 $936万
 $21,719/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -10156,7 +13080,7 @@
           <t>G | 426呎 (2房)
 $999万
 $23,447/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
     </row>
@@ -10171,7 +13095,7 @@
           <t>A | 598呎 (3房)
 $1310万
 $21,912/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -10179,7 +13103,7 @@
           <t>B | 282呎 (1房)
 $659万
 $23,359/呎
-(25年-11月)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -10219,7 +13143,7 @@
           <t>G | 426呎 (2房)
 $994万
 $23,324/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
     </row>
@@ -10242,7 +13166,7 @@
           <t>B | 244呎 (1房)
 $662万
 $27,143/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -10250,7 +13174,7 @@
           <t>C | 339呎 (2房)
 $930万
 $27,423/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">

--- a/files/港岛-湾仔-Woodis.xlsx
+++ b/files/港岛-湾仔-Woodis.xlsx
@@ -11914,7 +11914,7 @@
           <t>C | 377呎 (2房)
 $971万
 $25,753/呎
-(25年-11月-09日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -11977,7 +11977,7 @@
           <t>C | 377呎 (2房)
 $961万
 $25,499/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -11985,7 +11985,7 @@
           <t>D | 343呎 (2房)
 $847万
 $24,687/呎
-(25年-11月-25日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -11993,7 +11993,7 @@
           <t>E | 346呎 (2房)
 $862万
 $24,906/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -12001,7 +12001,7 @@
           <t>F | 431呎 (2房)
 $1217万
 $28,236/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -12024,7 +12024,7 @@
           <t>A | 598呎 (3房)
 $1875万
 $31,358/呎
-(25年-11月-19日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -12040,7 +12040,7 @@
           <t>C | 377呎 (2房)
 $922万
 $24,447/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -12048,7 +12048,7 @@
           <t>D | 343呎 (2房)
 $831万
 $24,217/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -12056,7 +12056,7 @@
           <t>E | 346呎 (2房)
 $900万
 $26,002/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -12064,7 +12064,7 @@
           <t>F | 431呎 (2房)
 $1177万
 $27,316/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -12072,7 +12072,7 @@
           <t>G | 426呎 (2房)
 $1270万
 $29,819/呎
-(25年-11月-20日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -12087,7 +12087,7 @@
           <t>A | 598呎 (3房)
 $1820万
 $30,441/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -12103,7 +12103,7 @@
           <t>C | 377呎 (2房)
 $945万
 $25,073/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -12111,7 +12111,7 @@
           <t>D | 343呎 (2房)
 $809万
 $23,600/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -12119,7 +12119,7 @@
           <t>E | 346呎 (2房)
 $840万
 $24,282/呎
-(25年-11月-16日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -12127,7 +12127,7 @@
           <t>F | 431呎 (2房)
 $1137万
 $26,373/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -12135,7 +12135,7 @@
           <t>G | 426呎 (2房)
 $1169万
 $27,438/呎
-(25年-11月-20日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -12166,7 +12166,7 @@
           <t>C | 377呎 (2房)
 $939万
 $24,904/呎
-(25年-11月-09日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -12174,7 +12174,7 @@
           <t>D | 343呎 (2房)
 $770万
 $22,464/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -12182,7 +12182,7 @@
           <t>E | 346呎 (2房)
 $782万
 $22,598/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -12190,7 +12190,7 @@
           <t>F | 431呎 (2房)
 $1119万
 $25,965/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -12198,7 +12198,7 @@
           <t>G | 426呎 (2房)
 $1194万
 $28,039/呎
-(25年-10月-24日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -12213,7 +12213,7 @@
           <t>A | 598呎 (3房)
 $1711万
 $28,607/呎
-(25年-11月-09日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -12229,7 +12229,7 @@
           <t>C | 377呎 (2房)
 $933万
 $24,735/呎
-(25年-11月-09日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -12237,7 +12237,7 @@
           <t>D | 343呎 (2房)
 $799万
 $23,283/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -12245,7 +12245,7 @@
           <t>E | 346呎 (2房)
 $774万
 $22,375/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -12253,7 +12253,7 @@
           <t>F | 431呎 (2房)
 $1108万
 $25,705/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -12261,7 +12261,7 @@
           <t>G | 426呎 (2房)
 $1121万
 $26,326/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -12276,7 +12276,7 @@
           <t>A | 598呎 (3房)
 $1545万
 $25,843/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -12292,7 +12292,7 @@
           <t>C | 377呎 (2房)
 $897万
 $23,788/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -12300,7 +12300,7 @@
           <t>D | 343呎 (2房)
 $758万
 $22,085/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -12308,7 +12308,7 @@
           <t>E | 346呎 (2房)
 $766万
 $22,149/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -12316,7 +12316,7 @@
           <t>F | 431呎 (2房)
 $1097万
 $25,447/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -12324,7 +12324,7 @@
           <t>G | 426呎 (2房)
 $1107万
 $25,976/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
           <t>A | 598呎 (3房)
 $1524万
 $25,480/呎
-(25年-11月-16日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -12355,7 +12355,7 @@
           <t>C | 377呎 (2房)
 $967万
 $25,655/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -12363,7 +12363,7 @@
           <t>D | 343呎 (2房)
 $750万
 $21,857/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -12371,7 +12371,7 @@
           <t>E | 346呎 (2房)
 $759万
 $21,923/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -12379,7 +12379,7 @@
           <t>F | 431呎 (2房)
 $1086万
 $25,189/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -12387,7 +12387,7 @@
           <t>G | 426呎 (2房)
 $1061万
 $24,903/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
           <t>A | 598呎 (3房)
 $1552万
 $25,952/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -12418,7 +12418,7 @@
           <t>C | 377呎 (2房)
 $884万
 $23,461/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -12426,7 +12426,7 @@
           <t>D | 343呎 (2房)
 $742万
 $21,632/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -12434,7 +12434,7 @@
           <t>E | 346呎 (2房)
 $751万
 $21,697/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -12442,7 +12442,7 @@
           <t>F | 431呎 (2房)
 $1041万
 $24,142/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -12450,7 +12450,7 @@
           <t>G | 426呎 (2房)
 $1081万
 $25,365/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -12465,7 +12465,7 @@
           <t>A | 598呎 (3房)
 $1482万
 $24,785/呎
-(25年-11月-09日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -12481,7 +12481,7 @@
           <t>C | 377呎 (2房)
 $905万
 $23,993/呎
-(25年-11月-19日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -12497,7 +12497,7 @@
           <t>E | 346呎 (2房)
 $746万
 $21,548/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -12505,7 +12505,7 @@
           <t>F | 431呎 (2房)
 $1030万
 $23,892/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -12513,7 +12513,7 @@
           <t>G | 426呎 (2房)
 $1077万
 $25,280/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -12528,7 +12528,7 @@
           <t>A | 598呎 (3房)
 $1472万
 $24,611/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -12544,7 +12544,7 @@
           <t>C | 377呎 (2房)
 $872万
 $23,132/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -12552,7 +12552,7 @@
           <t>D | 343呎 (2房)
 $755万
 $22,024/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -12560,7 +12560,7 @@
           <t>E | 346呎 (2房)
 $740万
 $21,397/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -12568,7 +12568,7 @@
           <t>F | 431呎 (2房)
 $1023万
 $23,726/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -12576,7 +12576,7 @@
           <t>G | 426呎 (2房)
 $1025万
 $24,058/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -12591,7 +12591,7 @@
           <t>A | 598呎 (3房)
 $1509万
 $25,234/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -12607,7 +12607,7 @@
           <t>C | 377呎 (2房)
 $866万
 $22,966/呎
-(25年-11月-06日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -12631,7 +12631,7 @@
           <t>F | 431呎 (2房)
 $1015万
 $23,557/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -12639,7 +12639,7 @@
           <t>G | 426呎 (2房)
 $1045万
 $24,533/呎
-(25年-10月-24日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -12654,7 +12654,7 @@
           <t>A | 598呎 (3房)
 $1509万
 $25,228/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -12662,7 +12662,7 @@
           <t>B | 282呎 (1房)
 $720万
 $25,533/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -12670,7 +12670,7 @@
           <t>C | 377呎 (2房)
 $885万
 $23,485/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -12678,7 +12678,7 @@
           <t>D | 343呎 (2房)
 $721万
 $21,026/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -12686,7 +12686,7 @@
           <t>E | 346呎 (2房)
 $730万
 $21,096/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -12694,7 +12694,7 @@
           <t>F | 431呎 (2房)
 $1008万
 $23,390/呎
-(25年-10月-17日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -12702,7 +12702,7 @@
           <t>G | 426呎 (2房)
 $1010万
 $23,719/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -12717,7 +12717,7 @@
           <t>A | 598呎 (3房)
 $1425万
 $23,829/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -12725,7 +12725,7 @@
           <t>B | 282呎 (1房)
 $715万
 $25,347/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -12733,7 +12733,7 @@
           <t>C | 377呎 (2房)
 $853万
 $22,639/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -12757,7 +12757,7 @@
           <t>F | 431呎 (2房)
 $1030万
 $23,895/呎
-(25年-10月-17日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -12765,7 +12765,7 @@
           <t>G | 426呎 (2房)
 $1030万
 $24,185/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -12780,7 +12780,7 @@
           <t>A | 598呎 (3房)
 $1399万
 $23,394/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -12788,7 +12788,7 @@
           <t>B | 282呎 (1房)
 $676万
 $23,966/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -12796,7 +12796,7 @@
           <t>C | 377呎 (2房)
 $874万
 $23,193/呎
-(25年-11月-18日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -12804,7 +12804,7 @@
           <t>D | 343呎 (2房)
 $734万
 $21,396/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -12812,7 +12812,7 @@
           <t>E | 346呎 (2房)
 $738万
 $21,320/呎
-(25年-10月-17日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -12820,7 +12820,7 @@
           <t>F | 431呎 (2房)
 $983万
 $22,806/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -12828,7 +12828,7 @@
           <t>G | 426呎 (2房)
 $996万
 $23,382/呎
-(25年-11月-16日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -12843,7 +12843,7 @@
           <t>A | 598呎 (3房)
 $1373万
 $22,965/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -12851,7 +12851,7 @@
           <t>B | 282呎 (1房)
 $710万
 $25,185/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -12859,7 +12859,7 @@
           <t>C | 377呎 (2房)
 $844万
 $22,395/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -12867,7 +12867,7 @@
           <t>D | 343呎 (2房)
 $706万
 $20,570/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -12875,7 +12875,7 @@
           <t>E | 346呎 (2房)
 $705万
 $20,389/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -12883,7 +12883,7 @@
           <t>F | 431呎 (2房)
 $1000万
 $23,206/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -12891,7 +12891,7 @@
           <t>G | 426呎 (2房)
 $989万
 $23,212/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -12906,7 +12906,7 @@
           <t>A | 598呎 (3房)
 $1347万
 $22,525/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -12914,7 +12914,7 @@
           <t>B | 282呎 (1房)
 $671万
 $23,806/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -12946,7 +12946,7 @@
           <t>F | 431呎 (2房)
 $951万
 $22,054/呎
-(25年-10月-17日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -12954,7 +12954,7 @@
           <t>G | 426呎 (2房)
 $1014万
 $23,795/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
           <t>A | 598呎 (3房)
 $1321万
 $22,089/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -12977,7 +12977,7 @@
           <t>B | 282呎 (1房)
 $669万
 $23,740/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -12985,7 +12985,7 @@
           <t>C | 377呎 (2房)
 $865万
 $22,954/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -13009,7 +13009,7 @@
           <t>F | 431呎 (2房)
 $943万
 $21,888/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -13017,7 +13017,7 @@
           <t>G | 426呎 (2房)
 $1006万
 $23,621/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -13032,7 +13032,7 @@
           <t>A | 598呎 (3房)
 $1337万
 $22,360/呎
-(25年-11月-06日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -13040,7 +13040,7 @@
           <t>B | 282呎 (1房)
 $664万
 $23,561/呎
-(25年-11月-16日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -13072,7 +13072,7 @@
           <t>F | 431呎 (2房)
 $936万
 $21,719/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -13080,7 +13080,7 @@
           <t>G | 426呎 (2房)
 $999万
 $23,447/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -13095,7 +13095,7 @@
           <t>A | 598呎 (3房)
 $1310万
 $21,912/呎
-(25年-11月-06日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -13103,7 +13103,7 @@
           <t>B | 282呎 (1房)
 $659万
 $23,359/呎
-(25年-11月-18日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -13143,7 +13143,7 @@
           <t>G | 426呎 (2房)
 $994万
 $23,324/呎
-(25年-11月-09日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -13166,7 +13166,7 @@
           <t>B | 244呎 (1房)
 $662万
 $27,143/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -13174,7 +13174,7 @@
           <t>C | 339呎 (2房)
 $930万
 $27,423/呎
-(25年-11月-20日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">

--- a/files/港岛-湾仔-Woodis.xlsx
+++ b/files/港岛-湾仔-Woodis.xlsx
@@ -11914,7 +11914,7 @@
           <t>C | 377呎 (2房)
 $971万
 $25,753/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -11977,7 +11977,7 @@
           <t>C | 377呎 (2房)
 $961万
 $25,499/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -11985,7 +11985,7 @@
           <t>D | 343呎 (2房)
 $847万
 $24,687/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -11993,7 +11993,7 @@
           <t>E | 346呎 (2房)
 $862万
 $24,906/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -12001,7 +12001,7 @@
           <t>F | 431呎 (2房)
 $1217万
 $28,236/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -12024,7 +12024,7 @@
           <t>A | 598呎 (3房)
 $1875万
 $31,358/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -12040,7 +12040,7 @@
           <t>C | 377呎 (2房)
 $922万
 $24,447/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -12048,7 +12048,7 @@
           <t>D | 343呎 (2房)
 $831万
 $24,217/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -12056,7 +12056,7 @@
           <t>E | 346呎 (2房)
 $900万
 $26,002/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -12064,7 +12064,7 @@
           <t>F | 431呎 (2房)
 $1177万
 $27,316/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -12072,7 +12072,7 @@
           <t>G | 426呎 (2房)
 $1270万
 $29,819/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
     </row>
@@ -12087,7 +12087,7 @@
           <t>A | 598呎 (3房)
 $1820万
 $30,441/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -12103,7 +12103,7 @@
           <t>C | 377呎 (2房)
 $945万
 $25,073/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -12111,7 +12111,7 @@
           <t>D | 343呎 (2房)
 $809万
 $23,600/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -12119,7 +12119,7 @@
           <t>E | 346呎 (2房)
 $840万
 $24,282/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -12127,7 +12127,7 @@
           <t>F | 431呎 (2房)
 $1137万
 $26,373/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -12135,7 +12135,7 @@
           <t>G | 426呎 (2房)
 $1169万
 $27,438/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
     </row>
@@ -12166,7 +12166,7 @@
           <t>C | 377呎 (2房)
 $939万
 $24,904/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -12174,7 +12174,7 @@
           <t>D | 343呎 (2房)
 $770万
 $22,464/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -12182,7 +12182,7 @@
           <t>E | 346呎 (2房)
 $782万
 $22,598/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -12190,7 +12190,7 @@
           <t>F | 431呎 (2房)
 $1119万
 $25,965/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -12198,7 +12198,7 @@
           <t>G | 426呎 (2房)
 $1194万
 $28,039/呎
-(25年-10月)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
     </row>
@@ -12213,7 +12213,7 @@
           <t>A | 598呎 (3房)
 $1711万
 $28,607/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -12229,7 +12229,7 @@
           <t>C | 377呎 (2房)
 $933万
 $24,735/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -12237,7 +12237,7 @@
           <t>D | 343呎 (2房)
 $799万
 $23,283/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -12245,7 +12245,7 @@
           <t>E | 346呎 (2房)
 $774万
 $22,375/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -12253,7 +12253,7 @@
           <t>F | 431呎 (2房)
 $1108万
 $25,705/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -12261,7 +12261,7 @@
           <t>G | 426呎 (2房)
 $1121万
 $26,326/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -12276,7 +12276,7 @@
           <t>A | 598呎 (3房)
 $1545万
 $25,843/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -12292,7 +12292,7 @@
           <t>C | 377呎 (2房)
 $897万
 $23,788/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -12300,7 +12300,7 @@
           <t>D | 343呎 (2房)
 $758万
 $22,085/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -12308,7 +12308,7 @@
           <t>E | 346呎 (2房)
 $766万
 $22,149/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -12316,7 +12316,7 @@
           <t>F | 431呎 (2房)
 $1097万
 $25,447/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -12324,7 +12324,7 @@
           <t>G | 426呎 (2房)
 $1107万
 $25,976/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
           <t>A | 598呎 (3房)
 $1524万
 $25,480/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -12355,7 +12355,7 @@
           <t>C | 377呎 (2房)
 $967万
 $25,655/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -12363,7 +12363,7 @@
           <t>D | 343呎 (2房)
 $750万
 $21,857/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -12371,7 +12371,7 @@
           <t>E | 346呎 (2房)
 $759万
 $21,923/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -12379,7 +12379,7 @@
           <t>F | 431呎 (2房)
 $1086万
 $25,189/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -12387,7 +12387,7 @@
           <t>G | 426呎 (2房)
 $1061万
 $24,903/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
           <t>A | 598呎 (3房)
 $1552万
 $25,952/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -12418,7 +12418,7 @@
           <t>C | 377呎 (2房)
 $884万
 $23,461/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -12426,7 +12426,7 @@
           <t>D | 343呎 (2房)
 $742万
 $21,632/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -12434,7 +12434,7 @@
           <t>E | 346呎 (2房)
 $751万
 $21,697/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -12442,7 +12442,7 @@
           <t>F | 431呎 (2房)
 $1041万
 $24,142/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -12450,7 +12450,7 @@
           <t>G | 426呎 (2房)
 $1081万
 $25,365/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -12465,7 +12465,7 @@
           <t>A | 598呎 (3房)
 $1482万
 $24,785/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -12481,7 +12481,7 @@
           <t>C | 377呎 (2房)
 $905万
 $23,993/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -12497,7 +12497,7 @@
           <t>E | 346呎 (2房)
 $746万
 $21,548/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -12505,7 +12505,7 @@
           <t>F | 431呎 (2房)
 $1030万
 $23,892/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -12513,7 +12513,7 @@
           <t>G | 426呎 (2房)
 $1077万
 $25,280/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -12528,7 +12528,7 @@
           <t>A | 598呎 (3房)
 $1472万
 $24,611/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -12544,7 +12544,7 @@
           <t>C | 377呎 (2房)
 $872万
 $23,132/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -12552,7 +12552,7 @@
           <t>D | 343呎 (2房)
 $755万
 $22,024/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -12560,7 +12560,7 @@
           <t>E | 346呎 (2房)
 $740万
 $21,397/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -12568,7 +12568,7 @@
           <t>F | 431呎 (2房)
 $1023万
 $23,726/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -12576,7 +12576,7 @@
           <t>G | 426呎 (2房)
 $1025万
 $24,058/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -12591,7 +12591,7 @@
           <t>A | 598呎 (3房)
 $1509万
 $25,234/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -12607,7 +12607,7 @@
           <t>C | 377呎 (2房)
 $866万
 $22,966/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -12631,7 +12631,7 @@
           <t>F | 431呎 (2房)
 $1015万
 $23,557/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -12639,7 +12639,7 @@
           <t>G | 426呎 (2房)
 $1045万
 $24,533/呎
-(25年-10月)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
     </row>
@@ -12654,7 +12654,7 @@
           <t>A | 598呎 (3房)
 $1509万
 $25,228/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -12662,7 +12662,7 @@
           <t>B | 282呎 (1房)
 $720万
 $25,533/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -12670,7 +12670,7 @@
           <t>C | 377呎 (2房)
 $885万
 $23,485/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -12678,7 +12678,7 @@
           <t>D | 343呎 (2房)
 $721万
 $21,026/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -12686,7 +12686,7 @@
           <t>E | 346呎 (2房)
 $730万
 $21,096/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -12694,7 +12694,7 @@
           <t>F | 431呎 (2房)
 $1008万
 $23,390/呎
-(25年-10月)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -12702,7 +12702,7 @@
           <t>G | 426呎 (2房)
 $1010万
 $23,719/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -12717,7 +12717,7 @@
           <t>A | 598呎 (3房)
 $1425万
 $23,829/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -12725,7 +12725,7 @@
           <t>B | 282呎 (1房)
 $715万
 $25,347/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -12733,7 +12733,7 @@
           <t>C | 377呎 (2房)
 $853万
 $22,639/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -12757,7 +12757,7 @@
           <t>F | 431呎 (2房)
 $1030万
 $23,895/呎
-(25年-10月)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -12765,7 +12765,7 @@
           <t>G | 426呎 (2房)
 $1030万
 $24,185/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -12780,7 +12780,7 @@
           <t>A | 598呎 (3房)
 $1399万
 $23,394/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -12788,7 +12788,7 @@
           <t>B | 282呎 (1房)
 $676万
 $23,966/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -12796,7 +12796,7 @@
           <t>C | 377呎 (2房)
 $874万
 $23,193/呎
-(25年-11月)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -12804,7 +12804,7 @@
           <t>D | 343呎 (2房)
 $734万
 $21,396/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -12812,7 +12812,7 @@
           <t>E | 346呎 (2房)
 $738万
 $21,320/呎
-(25年-10月)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -12820,7 +12820,7 @@
           <t>F | 431呎 (2房)
 $983万
 $22,806/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -12828,7 +12828,7 @@
           <t>G | 426呎 (2房)
 $996万
 $23,382/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
     </row>
@@ -12843,7 +12843,7 @@
           <t>A | 598呎 (3房)
 $1373万
 $22,965/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -12851,7 +12851,7 @@
           <t>B | 282呎 (1房)
 $710万
 $25,185/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -12859,7 +12859,7 @@
           <t>C | 377呎 (2房)
 $844万
 $22,395/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -12867,7 +12867,7 @@
           <t>D | 343呎 (2房)
 $706万
 $20,570/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -12875,7 +12875,7 @@
           <t>E | 346呎 (2房)
 $705万
 $20,389/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -12883,7 +12883,7 @@
           <t>F | 431呎 (2房)
 $1000万
 $23,206/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -12891,7 +12891,7 @@
           <t>G | 426呎 (2房)
 $989万
 $23,212/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
     </row>
@@ -12906,7 +12906,7 @@
           <t>A | 598呎 (3房)
 $1347万
 $22,525/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -12914,7 +12914,7 @@
           <t>B | 282呎 (1房)
 $671万
 $23,806/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -12946,7 +12946,7 @@
           <t>F | 431呎 (2房)
 $951万
 $22,054/呎
-(25年-10月)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -12954,7 +12954,7 @@
           <t>G | 426呎 (2房)
 $1014万
 $23,795/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
           <t>A | 598呎 (3房)
 $1321万
 $22,089/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -12977,7 +12977,7 @@
           <t>B | 282呎 (1房)
 $669万
 $23,740/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -12985,7 +12985,7 @@
           <t>C | 377呎 (2房)
 $865万
 $22,954/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -13009,7 +13009,7 @@
           <t>F | 431呎 (2房)
 $943万
 $21,888/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -13017,7 +13017,7 @@
           <t>G | 426呎 (2房)
 $1006万
 $23,621/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -13032,7 +13032,7 @@
           <t>A | 598呎 (3房)
 $1337万
 $22,360/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -13040,7 +13040,7 @@
           <t>B | 282呎 (1房)
 $664万
 $23,561/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -13072,7 +13072,7 @@
           <t>F | 431呎 (2房)
 $936万
 $21,719/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -13080,7 +13080,7 @@
           <t>G | 426呎 (2房)
 $999万
 $23,447/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
     </row>
@@ -13095,7 +13095,7 @@
           <t>A | 598呎 (3房)
 $1310万
 $21,912/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -13103,7 +13103,7 @@
           <t>B | 282呎 (1房)
 $659万
 $23,359/呎
-(25年-11月)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -13143,7 +13143,7 @@
           <t>G | 426呎 (2房)
 $994万
 $23,324/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
     </row>
@@ -13166,7 +13166,7 @@
           <t>B | 244呎 (1房)
 $662万
 $27,143/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -13174,7 +13174,7 @@
           <t>C | 339呎 (2房)
 $930万
 $27,423/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
